--- a/Mazandasht_INFO.xlsx
+++ b/Mazandasht_INFO.xlsx
@@ -11,16 +11,17 @@
     <sheet name="Company" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Banks" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Customers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Suppliers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Accounts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Staff" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PartyTypes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TxnTypes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Products_Buy" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Products_Sell" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Baskets" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Warehouses" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Lists" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Sellers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Suppliers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Accounts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Staff" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PartyTypes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TxnTypes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Products_Buy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Products_Sell" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Baskets" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Warehouses" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Lists" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="ListUnits">Lists!$A$7:$A$32</definedName>
@@ -28,29 +29,32 @@
     <definedName name="ListCategories">Lists!$C$7:$C$32</definedName>
     <definedName name="ListYesNo">Lists!$D$7:$D$8</definedName>
     <definedName name="ListPT">PartyTypes!$B$7:$B$26</definedName>
+    <definedName name="ListBaskets">OFFSET(Baskets!$E$7,0,0,MAX(COUNTIF(Baskets!$E$7:$E$36,"?*"),1),1)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Banks'!$5:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Banks'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Customers'!$5:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Customers'!$A$1:$G$206</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Suppliers'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Suppliers'!$A$1:$G$106</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Accounts'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Accounts'!$A$1:$D$56</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Staff'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Staff'!$A$1:$E$56</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'PartyTypes'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'PartyTypes'!$A$1:$D$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'TxnTypes'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'TxnTypes'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Products_Buy'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Products_Buy'!$A$1:$E$106</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Products_Sell'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Products_Sell'!$A$1:$E$106</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Baskets'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'Baskets'!$A$1:$D$36</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Warehouses'!$5:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'Warehouses'!$A$1:$E$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Lists'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Sellers'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Sellers'!$A$1:$G$106</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Suppliers'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Suppliers'!$A$1:$G$106</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Accounts'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Accounts'!$A$1:$D$56</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Staff'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Staff'!$A$1:$E$56</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'PartyTypes'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'PartyTypes'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'TxnTypes'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'TxnTypes'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Products_Buy'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Products_Buy'!$A$1:$E$106</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Products_Sell'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'Products_Sell'!$A$1:$F$106</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Baskets'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Baskets'!$A$1:$E$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Warehouses'!$5:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'Warehouses'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Lists'!$5:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -125,6 +129,11 @@
     </font>
     <font>
       <name val="Tahoma"/>
+      <color rgb="00607D8B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
       <b val="1"/>
       <color rgb="00E65100"/>
       <sz val="13"/>
@@ -163,11 +172,6 @@
       <name val="Consolas"/>
       <color rgb="00263238"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <color rgb="00607D8B"/>
-      <sz val="8.5"/>
     </font>
     <font>
       <name val="Tahoma"/>
@@ -292,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -300,19 +304,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="14" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -324,16 +328,16 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -379,6 +383,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -822,30 +829,40 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>فروشندگان</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>تأمین‌کنندگان</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>سایر حساب‌ها</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>کارکنان</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>محصولات خرید</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>محصولات فروش</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>سبدها</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>انبارها</t>
         </is>
@@ -861,26 +878,34 @@
         <v/>
       </c>
       <c r="C7" s="6">
+        <f>COUNTA(Sellers!$B$7:$B$106)</f>
+        <v/>
+      </c>
+      <c r="D7" s="6">
         <f>COUNTA(Suppliers!$C$7:$C$106)</f>
         <v/>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="6">
         <f>COUNTA(Accounts!$C$7:$C$56)</f>
         <v/>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <f>COUNTA(Staff!$B$7:$B$56)</f>
         <v/>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <f>COUNTA(Products_Buy!$B$7:$B$106)</f>
         <v/>
       </c>
-      <c r="G7" s="6">
+      <c r="H7" s="6">
         <f>COUNTA(Products_Sell!$B$7:$B$106)</f>
         <v/>
       </c>
-      <c r="H7" s="6">
+      <c r="I7" s="6">
+        <f>COUNTA(Baskets!$B$7:$B$36)</f>
+        <v/>
+      </c>
+      <c r="J7" s="6">
         <f>COUNTA(Warehouses!$B$7:$B$21)</f>
         <v/>
       </c>
@@ -956,12 +981,12 @@
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Suppliers</t>
+          <t>Sellers</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>تأمین‌کنندگان (حجره‌داران، باغ‌داران، عوامل) — کد S…</t>
+          <t>فروشندگان (خریداران-بازفروش‌ها) — کد SL… و نوع مشتری (کشویی)</t>
         </is>
       </c>
       <c r="C13" s="10" t="n"/>
@@ -974,12 +999,12 @@
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>Suppliers</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>سایر حساب‌ها (کارمزد، مالیات، صندوق و…) — کد X…</t>
+          <t>تأمین‌کنندگان (حجره‌داران، باغ‌داران، عوامل) — کد S…</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -992,12 +1017,12 @@
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>Accounts</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>کارکنان و فروشندگان — کد E…</t>
+          <t>سایر حساب‌ها (کارمزد، مالیات، صندوق و…) — کد X…</t>
         </is>
       </c>
       <c r="C15" s="10" t="n"/>
@@ -1010,12 +1035,12 @@
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>PartyTypes</t>
+          <t>Staff</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>انواع طرف حساب — منبع کشوی Entry</t>
+          <t>کارکنان و فروشندگان — کد E…</t>
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
@@ -1028,12 +1053,12 @@
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>TxnTypes</t>
+          <t>PartyTypes</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>انواع تراکنش — قابل توسعه برای ماهیت‌های آینده</t>
+          <t>انواع طرف حساب — منبع کشوی Entry</t>
         </is>
       </c>
       <c r="C17" s="10" t="n"/>
@@ -1046,12 +1071,12 @@
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Products_Buy</t>
+          <t>TxnTypes</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>محصولات خرید — کد PB…</t>
+          <t>انواع تراکنش — قابل توسعه برای ماهیت‌های آینده</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -1064,12 +1089,12 @@
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Products_Sell</t>
+          <t>Products_Buy</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>محصولات فروش — کد PS…</t>
+          <t>محصولات خرید — کد PB…</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -1082,12 +1107,12 @@
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Baskets</t>
+          <t>Products_Sell</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>انواع سبدها — کد BK…</t>
+          <t>محصولات فروش — کد PS…</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
@@ -1100,12 +1125,12 @@
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Baskets</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>انبارها — کد W…</t>
+          <t>انواع سبدها — کد BK…</t>
         </is>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -1118,12 +1143,12 @@
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>لیست‌های عمومی (واحد، سمت، دسته، بله/خیر)</t>
+          <t>انبارها — کد W…</t>
         </is>
       </c>
       <c r="C22" s="9" t="n"/>
@@ -1133,81 +1158,77 @@
       <c r="G22" s="9" t="n"/>
       <c r="H22" s="9" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>لیست‌های عمومی (واحد، سمت، دسته، بله/خیر)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>قواعد کدگذاری (در همه فایل‌ها یکسان است)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>قالب کد</t>
         </is>
       </c>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>نکته</t>
         </is>
       </c>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>بانک‌ها</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>BANK01 … BANK10</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>کد ثابت — عنوان آزاد</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="14" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>مشتریان</t>
+          <t>بانک‌ها</t>
         </is>
       </c>
       <c r="B28" s="12" t="n"/>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>C001, C002, …</t>
+          <t>BANK01 … BANK10</t>
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
       <c r="E28" s="13" t="n"/>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>کد ثابت پس از تعریف</t>
+          <t>کد ثابت — عنوان آزاد</t>
         </is>
       </c>
       <c r="G28" s="14" t="n"/>
@@ -1216,49 +1237,57 @@
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>تأمین‌کنندگان</t>
+          <t>مشتریان</t>
         </is>
       </c>
       <c r="B29" s="12" t="n"/>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>S001, S002, …</t>
+          <t>C001, C002, …</t>
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
       <c r="E29" s="13" t="n"/>
-      <c r="F29" s="14" t="inlineStr"/>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>کد ثابت پس از تعریف</t>
+        </is>
+      </c>
       <c r="G29" s="14" t="n"/>
       <c r="H29" s="14" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>سایر حساب‌ها</t>
+          <t>فروشندگان</t>
         </is>
       </c>
       <c r="B30" s="12" t="n"/>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>X001, X002, …</t>
+          <t>SL001, SL002, …</t>
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
       <c r="E30" s="13" t="n"/>
-      <c r="F30" s="14" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>منبع کد حساب فایل فروش</t>
+        </is>
+      </c>
       <c r="G30" s="14" t="n"/>
       <c r="H30" s="14" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>کارکنان/فروشندگان</t>
+          <t>تأمین‌کنندگان</t>
         </is>
       </c>
       <c r="B31" s="12" t="n"/>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>E001, E002, …</t>
+          <t>S001, S002, …</t>
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
@@ -1270,13 +1299,13 @@
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>انواع طرف حساب</t>
+          <t>سایر حساب‌ها</t>
         </is>
       </c>
       <c r="B32" s="12" t="n"/>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>PT01 …</t>
+          <t>X001, X002, …</t>
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
@@ -1288,13 +1317,13 @@
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>انواع تراکنش</t>
+          <t>کارکنان/فروشندگان</t>
         </is>
       </c>
       <c r="B33" s="12" t="n"/>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>T01 …</t>
+          <t>E001, E002, …</t>
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
@@ -1306,31 +1335,35 @@
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>محصولات خرید / فروش</t>
+          <t>انواع طرف حساب</t>
         </is>
       </c>
       <c r="B34" s="12" t="n"/>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>PB01… / PS01…</t>
+          <t>PT01 …</t>
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
       <c r="E34" s="13" t="n"/>
-      <c r="F34" s="14" t="inlineStr"/>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>حجره‌دار، صادراتی، واسطه، نقدی و… — قابل گسترش</t>
+        </is>
+      </c>
       <c r="G34" s="14" t="n"/>
       <c r="H34" s="14" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>سبدها / انبارها</t>
+          <t>انواع تراکنش</t>
         </is>
       </c>
       <c r="B35" s="12" t="n"/>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>BK01… / W01…</t>
+          <t>T01 …</t>
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
@@ -1339,52 +1372,64 @@
       <c r="G35" s="14" t="n"/>
       <c r="H35" s="14" t="n"/>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>محصولات خرید / فروش</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>PB01… / PS01…</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>محصول فروش: نوع سبد + نوع مرکبات دارد</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>سبدها / انبارها</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>BK01… / W01…</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>قواعد طلایی</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="n"/>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
-      <c r="H37" s="15" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>۱) هرگز کدها را تغییر ندهید؛ عنوان‌ها را آزادانه عوض کنید (سیستم با «کد» کار می‌کند، نه با عنوان).</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="16" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>۲) ردیف تازه = ردیف خالی آماده بعدی؛ کدها از قبل درج شده‌اند. بین ردیف‌ها ردیف خالی نگذارید.</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="17" t="n"/>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="17" t="n"/>
-      <c r="G39" s="17" t="n"/>
-      <c r="H39" s="17" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>۳) برای حذف، محتوای سلول‌ها را پاک کنید (Delete) — خودِ ردیف را حذف نکنید.</t>
+          <t>۱) هرگز کدها را تغییر ندهید؛ عنوان‌ها را آزادانه عوض کنید (سیستم با «کد» کار می‌کند، نه با عنوان).</t>
         </is>
       </c>
       <c r="B40" s="16" t="n"/>
@@ -1398,7 +1443,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>۴) این فایل و فایل تراکنش‌ها همیشه باید در یک پوشه باشند؛ مسیر لینک نسبی است.</t>
+          <t>۲) ردیف تازه = ردیف خالی آماده بعدی؛ کدها از قبل درج شده‌اند. بین ردیف‌ها ردیف خالی نگذارید.</t>
         </is>
       </c>
       <c r="B41" s="17" t="n"/>
@@ -1412,7 +1457,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>۵) بعد از تغییر در این فایل، در فایل تراکنش‌ها: Data ← Edit Links ← Update Values.</t>
+          <t>۳) برای حذف، محتوای سلول‌ها را پاک کنید (Delete) — خودِ ردیف را حذف نکنید.</t>
         </is>
       </c>
       <c r="B42" s="16" t="n"/>
@@ -1426,7 +1471,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>۶) تاریخ‌ها همیشه شمسی با قالب 1405/07/10 (یا 14050710) و ساعت با قالب 09:30 (یا 9:30).</t>
+          <t>۴) این فایل و فایل تراکنش‌ها همیشه باید در یک پوشه باشند؛ مسیر لینک نسبی است.</t>
         </is>
       </c>
       <c r="B43" s="17" t="n"/>
@@ -1440,7 +1485,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>۷) اعداد را با ارقام لاتین (انگلیسی) وارد کنید تا فرمول‌ها درست کار کنند.</t>
+          <t>۵) بعد از تغییر در این فایل، در فایل تراکنش‌ها: Data ← Edit Links ← Update Values.</t>
         </is>
       </c>
       <c r="B44" s="16" t="n"/>
@@ -1451,36 +1496,69 @@
       <c r="G44" s="16" t="n"/>
       <c r="H44" s="16" t="n"/>
     </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>۶) تاریخ‌ها همیشه شمسی با قالب 1405/07/10 (یا 14050710) و ساعت با قالب 09:30 (یا 9:30).</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="17" t="n"/>
+      <c r="H45" s="17" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>۷) اعداد را با ارقام لاتین (انگلیسی) وارد کنید تا فرمول‌ها درست کار کنند.</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="16" t="n"/>
+      <c r="H46" s="16" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="60">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A39:H39"/>
+    <mergeCell ref="F36:H36"/>
     <mergeCell ref="F33:H33"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="B20:H20"/>
+    <mergeCell ref="C36:E36"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="F27:H27"/>
     <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="B16:H16"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="F37:H37"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="B22:H22"/>
-    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="B18:H18"/>
+    <mergeCell ref="C37:E37"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A33:B33"/>
@@ -1491,17 +1569,16 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="C34:E34"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="F34:H34"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="F34:H34"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C26:E26"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="C29:E29"/>
@@ -1525,6 +1602,307 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0090A4AE"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>مازندشت — سورتینگ و بسته‌بندی مرکبات</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>باغدشت، بخش مرکزی، شهرستان قائم‌شهر، استان مازندران، ایران</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>انواع تراکنش (قابل توسعه برای ماهیت‌های آینده)</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>ستون نوع تراکنش در Entry فقط اطلاعاتی/تحلیلی است؛ واریز و برداشت از ستون‌های مبلغ خوانده می‌شود. در آینده می‌توانید ماهیت‌های تازه (انتقال، اصلاحیه و…) تعریف کنید.</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="n"/>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>عنوان</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>تأثیر بر مانده</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>توضیح</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Balance Effect</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>واریز</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>افزایش مانده</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>برداشت</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>کاهش مانده</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>انتقال بین بانکی</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>خنثی در مجموع</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>اصلاحیه / تعدیل</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>طبق ماهیت</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>سایر</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>طبق ماهیت</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.62" bottom="0.55" header="0.28" footer="0.25"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Tahoma"&amp;8 مازندشت — سامانه حساب‌های بانکی&amp;C&amp;"Tahoma"&amp;8 انواع تراکنش (قابل توسعه برای ماهیت‌های آینده)&amp;R&amp;"Tahoma"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Tahoma"&amp;7 باغدشت، بخش مرکزی، شهرستان قائم‌شهر، استان مازندران، ایران&amp;C&amp;"Tahoma"&amp;8 صفحه &amp;P از &amp;N&amp;R&amp;"Tahoma"&amp;7 چاپ: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00558B2F"/>
@@ -2820,21 +3198,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00558B2F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2847,6 +3226,7 @@
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -2858,6 +3238,7 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
@@ -2869,17 +3250,19 @@
       <c r="C3" s="18" t="n"/>
       <c r="D3" s="18" t="n"/>
       <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>کدها از PS01 شروع می‌شوند.</t>
+          <t>کدها از PS01 شروع می‌شوند. «نوع سبد» را از کشویی انتخاب کنید (از شیت Baskets) — در فایل فروش، با انتخاب هر محصول، نوع سبد و نوع مرکبات آن خودکار نوشته می‌شود.</t>
         </is>
       </c>
       <c r="B4" s="22" t="n"/>
       <c r="C4" s="22" t="n"/>
       <c r="D4" s="22" t="n"/>
       <c r="E4" s="22" t="n"/>
+      <c r="F4" s="22" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
@@ -2894,7 +3277,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>دسته</t>
+          <t>دسته (نوع مرکبات)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -2903,6 +3286,11 @@
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>نوع سبد</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>توضیحات</t>
         </is>
@@ -2931,6 +3319,11 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
+          <t>Basket</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -2958,6 +3351,11 @@
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
           <t>خروج خط سورتینگ</t>
         </is>
       </c>
@@ -2983,7 +3381,12 @@
           <t>کیلوگرم</t>
         </is>
       </c>
-      <c r="E8" s="28" t="n"/>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>BK02</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
@@ -3006,7 +3409,12 @@
           <t>کیلوگرم</t>
         </is>
       </c>
-      <c r="E9" s="26" t="n"/>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -3029,7 +3437,12 @@
           <t>کیلوگرم</t>
         </is>
       </c>
-      <c r="E10" s="28" t="n"/>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>BK01</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
@@ -3041,6 +3454,7 @@
       <c r="C11" s="26" t="n"/>
       <c r="D11" s="26" t="n"/>
       <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
@@ -3052,6 +3466,7 @@
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="28" t="n"/>
       <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
@@ -3063,6 +3478,7 @@
       <c r="C13" s="26" t="n"/>
       <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
@@ -3074,6 +3490,7 @@
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="28" t="n"/>
       <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
@@ -3085,6 +3502,7 @@
       <c r="C15" s="26" t="n"/>
       <c r="D15" s="26" t="n"/>
       <c r="E15" s="26" t="n"/>
+      <c r="F15" s="26" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
@@ -3096,6 +3514,7 @@
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
       <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
@@ -3107,6 +3526,7 @@
       <c r="C17" s="26" t="n"/>
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="26" t="n"/>
+      <c r="F17" s="26" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
@@ -3118,6 +3538,7 @@
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
@@ -3129,6 +3550,7 @@
       <c r="C19" s="26" t="n"/>
       <c r="D19" s="26" t="n"/>
       <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
@@ -3140,6 +3562,7 @@
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
       <c r="E20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
@@ -3151,6 +3574,7 @@
       <c r="C21" s="26" t="n"/>
       <c r="D21" s="26" t="n"/>
       <c r="E21" s="26" t="n"/>
+      <c r="F21" s="26" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
@@ -3162,6 +3586,7 @@
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
       <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
@@ -3173,6 +3598,7 @@
       <c r="C23" s="26" t="n"/>
       <c r="D23" s="26" t="n"/>
       <c r="E23" s="26" t="n"/>
+      <c r="F23" s="26" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
@@ -3184,6 +3610,7 @@
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
       <c r="E24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
@@ -3195,6 +3622,7 @@
       <c r="C25" s="26" t="n"/>
       <c r="D25" s="26" t="n"/>
       <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
@@ -3206,6 +3634,7 @@
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
@@ -3217,6 +3646,7 @@
       <c r="C27" s="26" t="n"/>
       <c r="D27" s="26" t="n"/>
       <c r="E27" s="26" t="n"/>
+      <c r="F27" s="26" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
@@ -3228,6 +3658,7 @@
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
       <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
@@ -3239,6 +3670,7 @@
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="26" t="n"/>
       <c r="E29" s="26" t="n"/>
+      <c r="F29" s="26" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
@@ -3250,6 +3682,7 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
       <c r="E30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
@@ -3261,6 +3694,7 @@
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
+      <c r="F31" s="26" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
@@ -3272,6 +3706,7 @@
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
       <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
@@ -3283,6 +3718,7 @@
       <c r="C33" s="26" t="n"/>
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="26" t="n"/>
+      <c r="F33" s="26" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="25" t="inlineStr">
@@ -3294,6 +3730,7 @@
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="25" t="inlineStr">
@@ -3305,6 +3742,7 @@
       <c r="C35" s="26" t="n"/>
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="26" t="n"/>
+      <c r="F35" s="26" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="25" t="inlineStr">
@@ -3316,6 +3754,7 @@
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
       <c r="E36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="25" t="inlineStr">
@@ -3327,6 +3766,7 @@
       <c r="C37" s="26" t="n"/>
       <c r="D37" s="26" t="n"/>
       <c r="E37" s="26" t="n"/>
+      <c r="F37" s="26" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="25" t="inlineStr">
@@ -3338,6 +3778,7 @@
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
@@ -3349,6 +3790,7 @@
       <c r="C39" s="26" t="n"/>
       <c r="D39" s="26" t="n"/>
       <c r="E39" s="26" t="n"/>
+      <c r="F39" s="26" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="25" t="inlineStr">
@@ -3360,6 +3802,7 @@
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="28" t="n"/>
       <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="25" t="inlineStr">
@@ -3371,6 +3814,7 @@
       <c r="C41" s="26" t="n"/>
       <c r="D41" s="26" t="n"/>
       <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="25" t="inlineStr">
@@ -3382,6 +3826,7 @@
       <c r="C42" s="28" t="n"/>
       <c r="D42" s="28" t="n"/>
       <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="25" t="inlineStr">
@@ -3393,6 +3838,7 @@
       <c r="C43" s="26" t="n"/>
       <c r="D43" s="26" t="n"/>
       <c r="E43" s="26" t="n"/>
+      <c r="F43" s="26" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="25" t="inlineStr">
@@ -3404,6 +3850,7 @@
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="28" t="n"/>
       <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="25" t="inlineStr">
@@ -3415,6 +3862,7 @@
       <c r="C45" s="26" t="n"/>
       <c r="D45" s="26" t="n"/>
       <c r="E45" s="26" t="n"/>
+      <c r="F45" s="26" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="25" t="inlineStr">
@@ -3426,6 +3874,7 @@
       <c r="C46" s="28" t="n"/>
       <c r="D46" s="28" t="n"/>
       <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="25" t="inlineStr">
@@ -3437,6 +3886,7 @@
       <c r="C47" s="26" t="n"/>
       <c r="D47" s="26" t="n"/>
       <c r="E47" s="26" t="n"/>
+      <c r="F47" s="26" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="25" t="inlineStr">
@@ -3448,6 +3898,7 @@
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="28" t="n"/>
       <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="25" t="inlineStr">
@@ -3459,6 +3910,7 @@
       <c r="C49" s="26" t="n"/>
       <c r="D49" s="26" t="n"/>
       <c r="E49" s="26" t="n"/>
+      <c r="F49" s="26" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="25" t="inlineStr">
@@ -3470,6 +3922,7 @@
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="28" t="n"/>
       <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="25" t="inlineStr">
@@ -3481,6 +3934,7 @@
       <c r="C51" s="26" t="n"/>
       <c r="D51" s="26" t="n"/>
       <c r="E51" s="26" t="n"/>
+      <c r="F51" s="26" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="25" t="inlineStr">
@@ -3492,6 +3946,7 @@
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="28" t="n"/>
       <c r="E52" s="28" t="n"/>
+      <c r="F52" s="28" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="25" t="inlineStr">
@@ -3503,6 +3958,7 @@
       <c r="C53" s="26" t="n"/>
       <c r="D53" s="26" t="n"/>
       <c r="E53" s="26" t="n"/>
+      <c r="F53" s="26" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="25" t="inlineStr">
@@ -3514,6 +3970,7 @@
       <c r="C54" s="28" t="n"/>
       <c r="D54" s="28" t="n"/>
       <c r="E54" s="28" t="n"/>
+      <c r="F54" s="28" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="25" t="inlineStr">
@@ -3525,6 +3982,7 @@
       <c r="C55" s="26" t="n"/>
       <c r="D55" s="26" t="n"/>
       <c r="E55" s="26" t="n"/>
+      <c r="F55" s="26" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="25" t="inlineStr">
@@ -3536,6 +3994,7 @@
       <c r="C56" s="28" t="n"/>
       <c r="D56" s="28" t="n"/>
       <c r="E56" s="28" t="n"/>
+      <c r="F56" s="28" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="25" t="inlineStr">
@@ -3547,6 +4006,7 @@
       <c r="C57" s="26" t="n"/>
       <c r="D57" s="26" t="n"/>
       <c r="E57" s="26" t="n"/>
+      <c r="F57" s="26" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="25" t="inlineStr">
@@ -3558,6 +4018,7 @@
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="28" t="n"/>
       <c r="E58" s="28" t="n"/>
+      <c r="F58" s="28" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="25" t="inlineStr">
@@ -3569,6 +4030,7 @@
       <c r="C59" s="26" t="n"/>
       <c r="D59" s="26" t="n"/>
       <c r="E59" s="26" t="n"/>
+      <c r="F59" s="26" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="25" t="inlineStr">
@@ -3580,6 +4042,7 @@
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="28" t="n"/>
       <c r="E60" s="28" t="n"/>
+      <c r="F60" s="28" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="25" t="inlineStr">
@@ -3591,6 +4054,7 @@
       <c r="C61" s="26" t="n"/>
       <c r="D61" s="26" t="n"/>
       <c r="E61" s="26" t="n"/>
+      <c r="F61" s="26" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="25" t="inlineStr">
@@ -3602,6 +4066,7 @@
       <c r="C62" s="28" t="n"/>
       <c r="D62" s="28" t="n"/>
       <c r="E62" s="28" t="n"/>
+      <c r="F62" s="28" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="25" t="inlineStr">
@@ -3613,6 +4078,7 @@
       <c r="C63" s="26" t="n"/>
       <c r="D63" s="26" t="n"/>
       <c r="E63" s="26" t="n"/>
+      <c r="F63" s="26" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="25" t="inlineStr">
@@ -3624,6 +4090,7 @@
       <c r="C64" s="28" t="n"/>
       <c r="D64" s="28" t="n"/>
       <c r="E64" s="28" t="n"/>
+      <c r="F64" s="28" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="25" t="inlineStr">
@@ -3635,6 +4102,7 @@
       <c r="C65" s="26" t="n"/>
       <c r="D65" s="26" t="n"/>
       <c r="E65" s="26" t="n"/>
+      <c r="F65" s="26" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="25" t="inlineStr">
@@ -3646,6 +4114,7 @@
       <c r="C66" s="28" t="n"/>
       <c r="D66" s="28" t="n"/>
       <c r="E66" s="28" t="n"/>
+      <c r="F66" s="28" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="25" t="inlineStr">
@@ -3657,6 +4126,7 @@
       <c r="C67" s="26" t="n"/>
       <c r="D67" s="26" t="n"/>
       <c r="E67" s="26" t="n"/>
+      <c r="F67" s="26" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="25" t="inlineStr">
@@ -3668,6 +4138,7 @@
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="28" t="n"/>
       <c r="E68" s="28" t="n"/>
+      <c r="F68" s="28" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="25" t="inlineStr">
@@ -3679,6 +4150,7 @@
       <c r="C69" s="26" t="n"/>
       <c r="D69" s="26" t="n"/>
       <c r="E69" s="26" t="n"/>
+      <c r="F69" s="26" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="25" t="inlineStr">
@@ -3690,6 +4162,7 @@
       <c r="C70" s="28" t="n"/>
       <c r="D70" s="28" t="n"/>
       <c r="E70" s="28" t="n"/>
+      <c r="F70" s="28" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="25" t="inlineStr">
@@ -3701,6 +4174,7 @@
       <c r="C71" s="26" t="n"/>
       <c r="D71" s="26" t="n"/>
       <c r="E71" s="26" t="n"/>
+      <c r="F71" s="26" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="25" t="inlineStr">
@@ -3712,6 +4186,7 @@
       <c r="C72" s="28" t="n"/>
       <c r="D72" s="28" t="n"/>
       <c r="E72" s="28" t="n"/>
+      <c r="F72" s="28" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="25" t="inlineStr">
@@ -3723,6 +4198,7 @@
       <c r="C73" s="26" t="n"/>
       <c r="D73" s="26" t="n"/>
       <c r="E73" s="26" t="n"/>
+      <c r="F73" s="26" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="25" t="inlineStr">
@@ -3734,6 +4210,7 @@
       <c r="C74" s="28" t="n"/>
       <c r="D74" s="28" t="n"/>
       <c r="E74" s="28" t="n"/>
+      <c r="F74" s="28" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="25" t="inlineStr">
@@ -3745,6 +4222,7 @@
       <c r="C75" s="26" t="n"/>
       <c r="D75" s="26" t="n"/>
       <c r="E75" s="26" t="n"/>
+      <c r="F75" s="26" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="25" t="inlineStr">
@@ -3756,6 +4234,7 @@
       <c r="C76" s="28" t="n"/>
       <c r="D76" s="28" t="n"/>
       <c r="E76" s="28" t="n"/>
+      <c r="F76" s="28" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="25" t="inlineStr">
@@ -3767,6 +4246,7 @@
       <c r="C77" s="26" t="n"/>
       <c r="D77" s="26" t="n"/>
       <c r="E77" s="26" t="n"/>
+      <c r="F77" s="26" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="25" t="inlineStr">
@@ -3778,6 +4258,7 @@
       <c r="C78" s="28" t="n"/>
       <c r="D78" s="28" t="n"/>
       <c r="E78" s="28" t="n"/>
+      <c r="F78" s="28" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="25" t="inlineStr">
@@ -3789,6 +4270,7 @@
       <c r="C79" s="26" t="n"/>
       <c r="D79" s="26" t="n"/>
       <c r="E79" s="26" t="n"/>
+      <c r="F79" s="26" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="25" t="inlineStr">
@@ -3800,6 +4282,7 @@
       <c r="C80" s="28" t="n"/>
       <c r="D80" s="28" t="n"/>
       <c r="E80" s="28" t="n"/>
+      <c r="F80" s="28" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="25" t="inlineStr">
@@ -3811,6 +4294,7 @@
       <c r="C81" s="26" t="n"/>
       <c r="D81" s="26" t="n"/>
       <c r="E81" s="26" t="n"/>
+      <c r="F81" s="26" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="25" t="inlineStr">
@@ -3822,6 +4306,7 @@
       <c r="C82" s="28" t="n"/>
       <c r="D82" s="28" t="n"/>
       <c r="E82" s="28" t="n"/>
+      <c r="F82" s="28" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="25" t="inlineStr">
@@ -3833,6 +4318,7 @@
       <c r="C83" s="26" t="n"/>
       <c r="D83" s="26" t="n"/>
       <c r="E83" s="26" t="n"/>
+      <c r="F83" s="26" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="25" t="inlineStr">
@@ -3844,6 +4330,7 @@
       <c r="C84" s="28" t="n"/>
       <c r="D84" s="28" t="n"/>
       <c r="E84" s="28" t="n"/>
+      <c r="F84" s="28" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="25" t="inlineStr">
@@ -3855,6 +4342,7 @@
       <c r="C85" s="26" t="n"/>
       <c r="D85" s="26" t="n"/>
       <c r="E85" s="26" t="n"/>
+      <c r="F85" s="26" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="25" t="inlineStr">
@@ -3866,6 +4354,7 @@
       <c r="C86" s="28" t="n"/>
       <c r="D86" s="28" t="n"/>
       <c r="E86" s="28" t="n"/>
+      <c r="F86" s="28" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="25" t="inlineStr">
@@ -3877,6 +4366,7 @@
       <c r="C87" s="26" t="n"/>
       <c r="D87" s="26" t="n"/>
       <c r="E87" s="26" t="n"/>
+      <c r="F87" s="26" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="25" t="inlineStr">
@@ -3888,6 +4378,7 @@
       <c r="C88" s="28" t="n"/>
       <c r="D88" s="28" t="n"/>
       <c r="E88" s="28" t="n"/>
+      <c r="F88" s="28" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="25" t="inlineStr">
@@ -3899,6 +4390,7 @@
       <c r="C89" s="26" t="n"/>
       <c r="D89" s="26" t="n"/>
       <c r="E89" s="26" t="n"/>
+      <c r="F89" s="26" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="25" t="inlineStr">
@@ -3910,6 +4402,7 @@
       <c r="C90" s="28" t="n"/>
       <c r="D90" s="28" t="n"/>
       <c r="E90" s="28" t="n"/>
+      <c r="F90" s="28" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="25" t="inlineStr">
@@ -3921,6 +4414,7 @@
       <c r="C91" s="26" t="n"/>
       <c r="D91" s="26" t="n"/>
       <c r="E91" s="26" t="n"/>
+      <c r="F91" s="26" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="25" t="inlineStr">
@@ -3932,6 +4426,7 @@
       <c r="C92" s="28" t="n"/>
       <c r="D92" s="28" t="n"/>
       <c r="E92" s="28" t="n"/>
+      <c r="F92" s="28" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="25" t="inlineStr">
@@ -3943,6 +4438,7 @@
       <c r="C93" s="26" t="n"/>
       <c r="D93" s="26" t="n"/>
       <c r="E93" s="26" t="n"/>
+      <c r="F93" s="26" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="25" t="inlineStr">
@@ -3954,6 +4450,7 @@
       <c r="C94" s="28" t="n"/>
       <c r="D94" s="28" t="n"/>
       <c r="E94" s="28" t="n"/>
+      <c r="F94" s="28" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="25" t="inlineStr">
@@ -3965,6 +4462,7 @@
       <c r="C95" s="26" t="n"/>
       <c r="D95" s="26" t="n"/>
       <c r="E95" s="26" t="n"/>
+      <c r="F95" s="26" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="25" t="inlineStr">
@@ -3976,6 +4474,7 @@
       <c r="C96" s="28" t="n"/>
       <c r="D96" s="28" t="n"/>
       <c r="E96" s="28" t="n"/>
+      <c r="F96" s="28" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="25" t="inlineStr">
@@ -3987,6 +4486,7 @@
       <c r="C97" s="26" t="n"/>
       <c r="D97" s="26" t="n"/>
       <c r="E97" s="26" t="n"/>
+      <c r="F97" s="26" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="25" t="inlineStr">
@@ -3998,6 +4498,7 @@
       <c r="C98" s="28" t="n"/>
       <c r="D98" s="28" t="n"/>
       <c r="E98" s="28" t="n"/>
+      <c r="F98" s="28" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="25" t="inlineStr">
@@ -4009,6 +4510,7 @@
       <c r="C99" s="26" t="n"/>
       <c r="D99" s="26" t="n"/>
       <c r="E99" s="26" t="n"/>
+      <c r="F99" s="26" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="25" t="inlineStr">
@@ -4020,6 +4522,7 @@
       <c r="C100" s="28" t="n"/>
       <c r="D100" s="28" t="n"/>
       <c r="E100" s="28" t="n"/>
+      <c r="F100" s="28" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="25" t="inlineStr">
@@ -4031,6 +4534,7 @@
       <c r="C101" s="26" t="n"/>
       <c r="D101" s="26" t="n"/>
       <c r="E101" s="26" t="n"/>
+      <c r="F101" s="26" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="25" t="inlineStr">
@@ -4042,6 +4546,7 @@
       <c r="C102" s="28" t="n"/>
       <c r="D102" s="28" t="n"/>
       <c r="E102" s="28" t="n"/>
+      <c r="F102" s="28" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="25" t="inlineStr">
@@ -4053,6 +4558,7 @@
       <c r="C103" s="26" t="n"/>
       <c r="D103" s="26" t="n"/>
       <c r="E103" s="26" t="n"/>
+      <c r="F103" s="26" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="25" t="inlineStr">
@@ -4064,6 +4570,7 @@
       <c r="C104" s="28" t="n"/>
       <c r="D104" s="28" t="n"/>
       <c r="E104" s="28" t="n"/>
+      <c r="F104" s="28" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="25" t="inlineStr">
@@ -4075,6 +4582,7 @@
       <c r="C105" s="26" t="n"/>
       <c r="D105" s="26" t="n"/>
       <c r="E105" s="26" t="n"/>
+      <c r="F105" s="26" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="25" t="inlineStr">
@@ -4086,20 +4594,24 @@
       <c r="C106" s="28" t="n"/>
       <c r="D106" s="28" t="n"/>
       <c r="E106" s="28" t="n"/>
+      <c r="F106" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="C7:C106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>ListCategories</formula1>
     </dataValidation>
     <dataValidation sqref="D7:D106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>ListUnits</formula1>
+    </dataValidation>
+    <dataValidation sqref="E7:E106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>ListBaskets</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -4116,20 +4628,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00558B2F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4141,6 +4654,7 @@
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -4151,6 +4665,7 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
@@ -4161,16 +4676,18 @@
       <c r="B3" s="18" t="n"/>
       <c r="C3" s="18" t="n"/>
       <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>کدها از BK01 شروع می‌شوند.</t>
+          <t>کدها از BK01 شروع می‌شوند. ستون آخر خودکار است و در کشوی «نوع سبد» محصولات استفاده می‌شود.</t>
         </is>
       </c>
       <c r="B4" s="22" t="n"/>
       <c r="C4" s="22" t="n"/>
       <c r="D4" s="22" t="n"/>
+      <c r="E4" s="22" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
@@ -4193,6 +4710,11 @@
           <t>توضیحات</t>
         </is>
       </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>برچسب کشویی (خودکار)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -4215,6 +4737,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>Label (auto)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
@@ -4235,6 +4762,10 @@
           <t>سبد پلاستیکی</t>
         </is>
       </c>
+      <c r="E7" s="30">
+        <f>IF($A7="","",$A7&amp;" – "&amp;IF($B7="","(بدون عنوان)",$B7))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
@@ -4255,6 +4786,10 @@
           <t>سبد پلاستیکی</t>
         </is>
       </c>
+      <c r="E8" s="30">
+        <f>IF($A8="","",$A8&amp;" – "&amp;IF($B8="","(بدون عنوان)",$B8))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
@@ -4274,6 +4809,10 @@
         <is>
           <t>کارتن</t>
         </is>
+      </c>
+      <c r="E9" s="30">
+        <f>IF($A9="","",$A9&amp;" – "&amp;IF($B9="","(بدون عنوان)",$B9))</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -4285,6 +4824,10 @@
       <c r="B10" s="28" t="n"/>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="28" t="n"/>
+      <c r="E10" s="30">
+        <f>IF($A10="","",$A10&amp;" – "&amp;IF($B10="","(بدون عنوان)",$B10))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
@@ -4295,6 +4838,10 @@
       <c r="B11" s="26" t="n"/>
       <c r="C11" s="26" t="n"/>
       <c r="D11" s="26" t="n"/>
+      <c r="E11" s="30">
+        <f>IF($A11="","",$A11&amp;" – "&amp;IF($B11="","(بدون عنوان)",$B11))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
@@ -4305,6 +4852,10 @@
       <c r="B12" s="28" t="n"/>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="28" t="n"/>
+      <c r="E12" s="30">
+        <f>IF($A12="","",$A12&amp;" – "&amp;IF($B12="","(بدون عنوان)",$B12))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
@@ -4315,6 +4866,10 @@
       <c r="B13" s="26" t="n"/>
       <c r="C13" s="26" t="n"/>
       <c r="D13" s="26" t="n"/>
+      <c r="E13" s="30">
+        <f>IF($A13="","",$A13&amp;" – "&amp;IF($B13="","(بدون عنوان)",$B13))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
@@ -4325,6 +4880,10 @@
       <c r="B14" s="28" t="n"/>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="28" t="n"/>
+      <c r="E14" s="30">
+        <f>IF($A14="","",$A14&amp;" – "&amp;IF($B14="","(بدون عنوان)",$B14))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
@@ -4335,6 +4894,10 @@
       <c r="B15" s="26" t="n"/>
       <c r="C15" s="26" t="n"/>
       <c r="D15" s="26" t="n"/>
+      <c r="E15" s="30">
+        <f>IF($A15="","",$A15&amp;" – "&amp;IF($B15="","(بدون عنوان)",$B15))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
@@ -4345,6 +4908,10 @@
       <c r="B16" s="28" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="28" t="n"/>
+      <c r="E16" s="30">
+        <f>IF($A16="","",$A16&amp;" – "&amp;IF($B16="","(بدون عنوان)",$B16))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
@@ -4355,6 +4922,10 @@
       <c r="B17" s="26" t="n"/>
       <c r="C17" s="26" t="n"/>
       <c r="D17" s="26" t="n"/>
+      <c r="E17" s="30">
+        <f>IF($A17="","",$A17&amp;" – "&amp;IF($B17="","(بدون عنوان)",$B17))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
@@ -4365,6 +4936,10 @@
       <c r="B18" s="28" t="n"/>
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="28" t="n"/>
+      <c r="E18" s="30">
+        <f>IF($A18="","",$A18&amp;" – "&amp;IF($B18="","(بدون عنوان)",$B18))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
@@ -4375,6 +4950,10 @@
       <c r="B19" s="26" t="n"/>
       <c r="C19" s="26" t="n"/>
       <c r="D19" s="26" t="n"/>
+      <c r="E19" s="30">
+        <f>IF($A19="","",$A19&amp;" – "&amp;IF($B19="","(بدون عنوان)",$B19))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
@@ -4385,6 +4964,10 @@
       <c r="B20" s="28" t="n"/>
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="28" t="n"/>
+      <c r="E20" s="30">
+        <f>IF($A20="","",$A20&amp;" – "&amp;IF($B20="","(بدون عنوان)",$B20))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
@@ -4395,6 +4978,10 @@
       <c r="B21" s="26" t="n"/>
       <c r="C21" s="26" t="n"/>
       <c r="D21" s="26" t="n"/>
+      <c r="E21" s="30">
+        <f>IF($A21="","",$A21&amp;" – "&amp;IF($B21="","(بدون عنوان)",$B21))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
@@ -4405,6 +4992,10 @@
       <c r="B22" s="28" t="n"/>
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="28" t="n"/>
+      <c r="E22" s="30">
+        <f>IF($A22="","",$A22&amp;" – "&amp;IF($B22="","(بدون عنوان)",$B22))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
@@ -4415,6 +5006,10 @@
       <c r="B23" s="26" t="n"/>
       <c r="C23" s="26" t="n"/>
       <c r="D23" s="26" t="n"/>
+      <c r="E23" s="30">
+        <f>IF($A23="","",$A23&amp;" – "&amp;IF($B23="","(بدون عنوان)",$B23))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
@@ -4425,6 +5020,10 @@
       <c r="B24" s="28" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="28" t="n"/>
+      <c r="E24" s="30">
+        <f>IF($A24="","",$A24&amp;" – "&amp;IF($B24="","(بدون عنوان)",$B24))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
@@ -4435,6 +5034,10 @@
       <c r="B25" s="26" t="n"/>
       <c r="C25" s="26" t="n"/>
       <c r="D25" s="26" t="n"/>
+      <c r="E25" s="30">
+        <f>IF($A25="","",$A25&amp;" – "&amp;IF($B25="","(بدون عنوان)",$B25))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
@@ -4445,6 +5048,10 @@
       <c r="B26" s="28" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
+      <c r="E26" s="30">
+        <f>IF($A26="","",$A26&amp;" – "&amp;IF($B26="","(بدون عنوان)",$B26))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
@@ -4455,6 +5062,10 @@
       <c r="B27" s="26" t="n"/>
       <c r="C27" s="26" t="n"/>
       <c r="D27" s="26" t="n"/>
+      <c r="E27" s="30">
+        <f>IF($A27="","",$A27&amp;" – "&amp;IF($B27="","(بدون عنوان)",$B27))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
@@ -4465,6 +5076,10 @@
       <c r="B28" s="28" t="n"/>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="n"/>
+      <c r="E28" s="30">
+        <f>IF($A28="","",$A28&amp;" – "&amp;IF($B28="","(بدون عنوان)",$B28))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
@@ -4475,6 +5090,10 @@
       <c r="B29" s="26" t="n"/>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="26" t="n"/>
+      <c r="E29" s="30">
+        <f>IF($A29="","",$A29&amp;" – "&amp;IF($B29="","(بدون عنوان)",$B29))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
@@ -4485,6 +5104,10 @@
       <c r="B30" s="28" t="n"/>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
+      <c r="E30" s="30">
+        <f>IF($A30="","",$A30&amp;" – "&amp;IF($B30="","(بدون عنوان)",$B30))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
@@ -4495,6 +5118,10 @@
       <c r="B31" s="26" t="n"/>
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="26" t="n"/>
+      <c r="E31" s="30">
+        <f>IF($A31="","",$A31&amp;" – "&amp;IF($B31="","(بدون عنوان)",$B31))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
@@ -4505,6 +5132,10 @@
       <c r="B32" s="28" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="n"/>
+      <c r="E32" s="30">
+        <f>IF($A32="","",$A32&amp;" – "&amp;IF($B32="","(بدون عنوان)",$B32))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
@@ -4515,6 +5146,10 @@
       <c r="B33" s="26" t="n"/>
       <c r="C33" s="26" t="n"/>
       <c r="D33" s="26" t="n"/>
+      <c r="E33" s="30">
+        <f>IF($A33="","",$A33&amp;" – "&amp;IF($B33="","(بدون عنوان)",$B33))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="25" t="inlineStr">
@@ -4525,6 +5160,10 @@
       <c r="B34" s="28" t="n"/>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
+      <c r="E34" s="30">
+        <f>IF($A34="","",$A34&amp;" – "&amp;IF($B34="","(بدون عنوان)",$B34))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="25" t="inlineStr">
@@ -4535,6 +5174,10 @@
       <c r="B35" s="26" t="n"/>
       <c r="C35" s="26" t="n"/>
       <c r="D35" s="26" t="n"/>
+      <c r="E35" s="30">
+        <f>IF($A35="","",$A35&amp;" – "&amp;IF($B35="","(بدون عنوان)",$B35))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="25" t="inlineStr">
@@ -4545,13 +5188,17 @@
       <c r="B36" s="28" t="n"/>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="28" t="n"/>
+      <c r="E36" s="30">
+        <f>IF($A36="","",$A36&amp;" – "&amp;IF($B36="","(بدون عنوان)",$B36))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.62" bottom="0.55" header="0.28" footer="0.25"/>
@@ -4567,7 +5214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00558B2F"/>
@@ -4917,7 +5564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0090A4AE"/>
@@ -8620,6 +9267,1573 @@
   <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>مازندشت — سورتینگ و بسته‌بندی مرکبات</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>باغدشت، بخش مرکزی، شهرستان قائم‌شهر، استان مازندران، ایران</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>دفتر فروشندگان (خریداران-بازفروش‌ها) — منبع کد حساب در فایل فروش</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>کدها از SL001 شروع می‌شوند و از قبل درج شده‌اند. «نوع مشتری» را از کشویی انتخاب کنید — انواع آن در شیت PartyTypes تعریف می‌شود (حجره‌دار، صادراتی، واسطه، نقدی و…) و هر زمان قابل گسترش است.</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="n"/>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="22" t="n"/>
+      <c r="F4" s="22" t="n"/>
+      <c r="G4" s="22" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>نام صاحب حساب</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>نوع مشتری</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>تلفن</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>همراه</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>نشانی</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>توضیحات</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Account Holder</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Customer Type</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>SL001</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>حاج رضا محمدی (نمونه)</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>حجره‌دار میدان بار</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>021-55550001</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>09120000001</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>تهران — میدان بار میوه و تره‌بار</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>نمونه — ویرایش کنید</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>SL002</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>شرکت گلسرای شمال (نمونه)</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>مشتری صادراتی</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>011-55550002</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>09120000002</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>ساری — شهرک صنعتی</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>نمونه</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>SL003</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>عباس نیک‌پی (نمونه — واسطه)</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>واسطه</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>011-55550003</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>09120000003</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>قائم‌شهر</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>نمونه</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>SL004</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>مشتری نقدی — پاساژ مرکزی (نمونه)</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>مشتری نقدی</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>011-55550004</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>09120000004</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>قائم‌شهر — پاساژ مرکزی</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>نمونه</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>SL005</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>SL006</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>SL007</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>SL008</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>SL009</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="26" t="n"/>
+      <c r="G15" s="26" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>SL010</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>SL011</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="26" t="n"/>
+      <c r="G17" s="26" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>SL012</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>SL013</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>SL014</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>SL015</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>SL016</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>SL017</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="26" t="n"/>
+      <c r="G23" s="26" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>SL018</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>SL019</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>SL020</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>SL021</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="26" t="n"/>
+      <c r="F27" s="26" t="n"/>
+      <c r="G27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>SL022</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>SL023</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="26" t="n"/>
+      <c r="F29" s="26" t="n"/>
+      <c r="G29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>SL024</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="28" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>SL025</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="26" t="n"/>
+      <c r="G31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>SL026</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>SL027</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="26" t="n"/>
+      <c r="G33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>SL028</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>SL029</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="26" t="n"/>
+      <c r="G35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>SL030</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="n"/>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="28" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>SL031</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+      <c r="E37" s="26" t="n"/>
+      <c r="F37" s="26" t="n"/>
+      <c r="G37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>SL032</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>SL033</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="26" t="n"/>
+      <c r="F39" s="26" t="n"/>
+      <c r="G39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>SL034</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>SL035</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
+      <c r="G41" s="26" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>SL036</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>SL037</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+      <c r="E43" s="26" t="n"/>
+      <c r="F43" s="26" t="n"/>
+      <c r="G43" s="26" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>SL038</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="n"/>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>SL039</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="n"/>
+      <c r="C45" s="26" t="n"/>
+      <c r="D45" s="26" t="n"/>
+      <c r="E45" s="26" t="n"/>
+      <c r="F45" s="26" t="n"/>
+      <c r="G45" s="26" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>SL040</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="n"/>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>SL041</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="n"/>
+      <c r="C47" s="26" t="n"/>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="26" t="n"/>
+      <c r="G47" s="26" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>SL042</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="n"/>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="28" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>SL043</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="26" t="n"/>
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="26" t="n"/>
+      <c r="G49" s="26" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>SL044</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="n"/>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="28" t="n"/>
+      <c r="G50" s="28" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>SL045</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="n"/>
+      <c r="C51" s="26" t="n"/>
+      <c r="D51" s="26" t="n"/>
+      <c r="E51" s="26" t="n"/>
+      <c r="F51" s="26" t="n"/>
+      <c r="G51" s="26" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>SL046</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="n"/>
+      <c r="C52" s="28" t="n"/>
+      <c r="D52" s="28" t="n"/>
+      <c r="E52" s="28" t="n"/>
+      <c r="F52" s="28" t="n"/>
+      <c r="G52" s="28" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>SL047</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="n"/>
+      <c r="C53" s="26" t="n"/>
+      <c r="D53" s="26" t="n"/>
+      <c r="E53" s="26" t="n"/>
+      <c r="F53" s="26" t="n"/>
+      <c r="G53" s="26" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>SL048</t>
+        </is>
+      </c>
+      <c r="B54" s="28" t="n"/>
+      <c r="C54" s="28" t="n"/>
+      <c r="D54" s="28" t="n"/>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="28" t="n"/>
+      <c r="G54" s="28" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>SL049</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="n"/>
+      <c r="C55" s="26" t="n"/>
+      <c r="D55" s="26" t="n"/>
+      <c r="E55" s="26" t="n"/>
+      <c r="F55" s="26" t="n"/>
+      <c r="G55" s="26" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>SL050</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="n"/>
+      <c r="C56" s="28" t="n"/>
+      <c r="D56" s="28" t="n"/>
+      <c r="E56" s="28" t="n"/>
+      <c r="F56" s="28" t="n"/>
+      <c r="G56" s="28" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>SL051</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="n"/>
+      <c r="C57" s="26" t="n"/>
+      <c r="D57" s="26" t="n"/>
+      <c r="E57" s="26" t="n"/>
+      <c r="F57" s="26" t="n"/>
+      <c r="G57" s="26" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>SL052</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="n"/>
+      <c r="C58" s="28" t="n"/>
+      <c r="D58" s="28" t="n"/>
+      <c r="E58" s="28" t="n"/>
+      <c r="F58" s="28" t="n"/>
+      <c r="G58" s="28" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>SL053</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="n"/>
+      <c r="C59" s="26" t="n"/>
+      <c r="D59" s="26" t="n"/>
+      <c r="E59" s="26" t="n"/>
+      <c r="F59" s="26" t="n"/>
+      <c r="G59" s="26" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>SL054</t>
+        </is>
+      </c>
+      <c r="B60" s="28" t="n"/>
+      <c r="C60" s="28" t="n"/>
+      <c r="D60" s="28" t="n"/>
+      <c r="E60" s="28" t="n"/>
+      <c r="F60" s="28" t="n"/>
+      <c r="G60" s="28" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>SL055</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="n"/>
+      <c r="C61" s="26" t="n"/>
+      <c r="D61" s="26" t="n"/>
+      <c r="E61" s="26" t="n"/>
+      <c r="F61" s="26" t="n"/>
+      <c r="G61" s="26" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>SL056</t>
+        </is>
+      </c>
+      <c r="B62" s="28" t="n"/>
+      <c r="C62" s="28" t="n"/>
+      <c r="D62" s="28" t="n"/>
+      <c r="E62" s="28" t="n"/>
+      <c r="F62" s="28" t="n"/>
+      <c r="G62" s="28" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>SL057</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="n"/>
+      <c r="C63" s="26" t="n"/>
+      <c r="D63" s="26" t="n"/>
+      <c r="E63" s="26" t="n"/>
+      <c r="F63" s="26" t="n"/>
+      <c r="G63" s="26" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>SL058</t>
+        </is>
+      </c>
+      <c r="B64" s="28" t="n"/>
+      <c r="C64" s="28" t="n"/>
+      <c r="D64" s="28" t="n"/>
+      <c r="E64" s="28" t="n"/>
+      <c r="F64" s="28" t="n"/>
+      <c r="G64" s="28" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>SL059</t>
+        </is>
+      </c>
+      <c r="B65" s="26" t="n"/>
+      <c r="C65" s="26" t="n"/>
+      <c r="D65" s="26" t="n"/>
+      <c r="E65" s="26" t="n"/>
+      <c r="F65" s="26" t="n"/>
+      <c r="G65" s="26" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>SL060</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="n"/>
+      <c r="C66" s="28" t="n"/>
+      <c r="D66" s="28" t="n"/>
+      <c r="E66" s="28" t="n"/>
+      <c r="F66" s="28" t="n"/>
+      <c r="G66" s="28" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>SL061</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="n"/>
+      <c r="C67" s="26" t="n"/>
+      <c r="D67" s="26" t="n"/>
+      <c r="E67" s="26" t="n"/>
+      <c r="F67" s="26" t="n"/>
+      <c r="G67" s="26" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>SL062</t>
+        </is>
+      </c>
+      <c r="B68" s="28" t="n"/>
+      <c r="C68" s="28" t="n"/>
+      <c r="D68" s="28" t="n"/>
+      <c r="E68" s="28" t="n"/>
+      <c r="F68" s="28" t="n"/>
+      <c r="G68" s="28" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>SL063</t>
+        </is>
+      </c>
+      <c r="B69" s="26" t="n"/>
+      <c r="C69" s="26" t="n"/>
+      <c r="D69" s="26" t="n"/>
+      <c r="E69" s="26" t="n"/>
+      <c r="F69" s="26" t="n"/>
+      <c r="G69" s="26" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>SL064</t>
+        </is>
+      </c>
+      <c r="B70" s="28" t="n"/>
+      <c r="C70" s="28" t="n"/>
+      <c r="D70" s="28" t="n"/>
+      <c r="E70" s="28" t="n"/>
+      <c r="F70" s="28" t="n"/>
+      <c r="G70" s="28" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>SL065</t>
+        </is>
+      </c>
+      <c r="B71" s="26" t="n"/>
+      <c r="C71" s="26" t="n"/>
+      <c r="D71" s="26" t="n"/>
+      <c r="E71" s="26" t="n"/>
+      <c r="F71" s="26" t="n"/>
+      <c r="G71" s="26" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="25" t="inlineStr">
+        <is>
+          <t>SL066</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="n"/>
+      <c r="C72" s="28" t="n"/>
+      <c r="D72" s="28" t="n"/>
+      <c r="E72" s="28" t="n"/>
+      <c r="F72" s="28" t="n"/>
+      <c r="G72" s="28" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>SL067</t>
+        </is>
+      </c>
+      <c r="B73" s="26" t="n"/>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="26" t="n"/>
+      <c r="E73" s="26" t="n"/>
+      <c r="F73" s="26" t="n"/>
+      <c r="G73" s="26" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>SL068</t>
+        </is>
+      </c>
+      <c r="B74" s="28" t="n"/>
+      <c r="C74" s="28" t="n"/>
+      <c r="D74" s="28" t="n"/>
+      <c r="E74" s="28" t="n"/>
+      <c r="F74" s="28" t="n"/>
+      <c r="G74" s="28" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>SL069</t>
+        </is>
+      </c>
+      <c r="B75" s="26" t="n"/>
+      <c r="C75" s="26" t="n"/>
+      <c r="D75" s="26" t="n"/>
+      <c r="E75" s="26" t="n"/>
+      <c r="F75" s="26" t="n"/>
+      <c r="G75" s="26" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>SL070</t>
+        </is>
+      </c>
+      <c r="B76" s="28" t="n"/>
+      <c r="C76" s="28" t="n"/>
+      <c r="D76" s="28" t="n"/>
+      <c r="E76" s="28" t="n"/>
+      <c r="F76" s="28" t="n"/>
+      <c r="G76" s="28" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="25" t="inlineStr">
+        <is>
+          <t>SL071</t>
+        </is>
+      </c>
+      <c r="B77" s="26" t="n"/>
+      <c r="C77" s="26" t="n"/>
+      <c r="D77" s="26" t="n"/>
+      <c r="E77" s="26" t="n"/>
+      <c r="F77" s="26" t="n"/>
+      <c r="G77" s="26" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>SL072</t>
+        </is>
+      </c>
+      <c r="B78" s="28" t="n"/>
+      <c r="C78" s="28" t="n"/>
+      <c r="D78" s="28" t="n"/>
+      <c r="E78" s="28" t="n"/>
+      <c r="F78" s="28" t="n"/>
+      <c r="G78" s="28" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>SL073</t>
+        </is>
+      </c>
+      <c r="B79" s="26" t="n"/>
+      <c r="C79" s="26" t="n"/>
+      <c r="D79" s="26" t="n"/>
+      <c r="E79" s="26" t="n"/>
+      <c r="F79" s="26" t="n"/>
+      <c r="G79" s="26" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>SL074</t>
+        </is>
+      </c>
+      <c r="B80" s="28" t="n"/>
+      <c r="C80" s="28" t="n"/>
+      <c r="D80" s="28" t="n"/>
+      <c r="E80" s="28" t="n"/>
+      <c r="F80" s="28" t="n"/>
+      <c r="G80" s="28" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>SL075</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="n"/>
+      <c r="C81" s="26" t="n"/>
+      <c r="D81" s="26" t="n"/>
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="26" t="n"/>
+      <c r="G81" s="26" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="25" t="inlineStr">
+        <is>
+          <t>SL076</t>
+        </is>
+      </c>
+      <c r="B82" s="28" t="n"/>
+      <c r="C82" s="28" t="n"/>
+      <c r="D82" s="28" t="n"/>
+      <c r="E82" s="28" t="n"/>
+      <c r="F82" s="28" t="n"/>
+      <c r="G82" s="28" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>SL077</t>
+        </is>
+      </c>
+      <c r="B83" s="26" t="n"/>
+      <c r="C83" s="26" t="n"/>
+      <c r="D83" s="26" t="n"/>
+      <c r="E83" s="26" t="n"/>
+      <c r="F83" s="26" t="n"/>
+      <c r="G83" s="26" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="25" t="inlineStr">
+        <is>
+          <t>SL078</t>
+        </is>
+      </c>
+      <c r="B84" s="28" t="n"/>
+      <c r="C84" s="28" t="n"/>
+      <c r="D84" s="28" t="n"/>
+      <c r="E84" s="28" t="n"/>
+      <c r="F84" s="28" t="n"/>
+      <c r="G84" s="28" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>SL079</t>
+        </is>
+      </c>
+      <c r="B85" s="26" t="n"/>
+      <c r="C85" s="26" t="n"/>
+      <c r="D85" s="26" t="n"/>
+      <c r="E85" s="26" t="n"/>
+      <c r="F85" s="26" t="n"/>
+      <c r="G85" s="26" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="25" t="inlineStr">
+        <is>
+          <t>SL080</t>
+        </is>
+      </c>
+      <c r="B86" s="28" t="n"/>
+      <c r="C86" s="28" t="n"/>
+      <c r="D86" s="28" t="n"/>
+      <c r="E86" s="28" t="n"/>
+      <c r="F86" s="28" t="n"/>
+      <c r="G86" s="28" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="25" t="inlineStr">
+        <is>
+          <t>SL081</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="n"/>
+      <c r="C87" s="26" t="n"/>
+      <c r="D87" s="26" t="n"/>
+      <c r="E87" s="26" t="n"/>
+      <c r="F87" s="26" t="n"/>
+      <c r="G87" s="26" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="25" t="inlineStr">
+        <is>
+          <t>SL082</t>
+        </is>
+      </c>
+      <c r="B88" s="28" t="n"/>
+      <c r="C88" s="28" t="n"/>
+      <c r="D88" s="28" t="n"/>
+      <c r="E88" s="28" t="n"/>
+      <c r="F88" s="28" t="n"/>
+      <c r="G88" s="28" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="25" t="inlineStr">
+        <is>
+          <t>SL083</t>
+        </is>
+      </c>
+      <c r="B89" s="26" t="n"/>
+      <c r="C89" s="26" t="n"/>
+      <c r="D89" s="26" t="n"/>
+      <c r="E89" s="26" t="n"/>
+      <c r="F89" s="26" t="n"/>
+      <c r="G89" s="26" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="25" t="inlineStr">
+        <is>
+          <t>SL084</t>
+        </is>
+      </c>
+      <c r="B90" s="28" t="n"/>
+      <c r="C90" s="28" t="n"/>
+      <c r="D90" s="28" t="n"/>
+      <c r="E90" s="28" t="n"/>
+      <c r="F90" s="28" t="n"/>
+      <c r="G90" s="28" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="25" t="inlineStr">
+        <is>
+          <t>SL085</t>
+        </is>
+      </c>
+      <c r="B91" s="26" t="n"/>
+      <c r="C91" s="26" t="n"/>
+      <c r="D91" s="26" t="n"/>
+      <c r="E91" s="26" t="n"/>
+      <c r="F91" s="26" t="n"/>
+      <c r="G91" s="26" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="25" t="inlineStr">
+        <is>
+          <t>SL086</t>
+        </is>
+      </c>
+      <c r="B92" s="28" t="n"/>
+      <c r="C92" s="28" t="n"/>
+      <c r="D92" s="28" t="n"/>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="28" t="n"/>
+      <c r="G92" s="28" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="25" t="inlineStr">
+        <is>
+          <t>SL087</t>
+        </is>
+      </c>
+      <c r="B93" s="26" t="n"/>
+      <c r="C93" s="26" t="n"/>
+      <c r="D93" s="26" t="n"/>
+      <c r="E93" s="26" t="n"/>
+      <c r="F93" s="26" t="n"/>
+      <c r="G93" s="26" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="25" t="inlineStr">
+        <is>
+          <t>SL088</t>
+        </is>
+      </c>
+      <c r="B94" s="28" t="n"/>
+      <c r="C94" s="28" t="n"/>
+      <c r="D94" s="28" t="n"/>
+      <c r="E94" s="28" t="n"/>
+      <c r="F94" s="28" t="n"/>
+      <c r="G94" s="28" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="25" t="inlineStr">
+        <is>
+          <t>SL089</t>
+        </is>
+      </c>
+      <c r="B95" s="26" t="n"/>
+      <c r="C95" s="26" t="n"/>
+      <c r="D95" s="26" t="n"/>
+      <c r="E95" s="26" t="n"/>
+      <c r="F95" s="26" t="n"/>
+      <c r="G95" s="26" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="25" t="inlineStr">
+        <is>
+          <t>SL090</t>
+        </is>
+      </c>
+      <c r="B96" s="28" t="n"/>
+      <c r="C96" s="28" t="n"/>
+      <c r="D96" s="28" t="n"/>
+      <c r="E96" s="28" t="n"/>
+      <c r="F96" s="28" t="n"/>
+      <c r="G96" s="28" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="25" t="inlineStr">
+        <is>
+          <t>SL091</t>
+        </is>
+      </c>
+      <c r="B97" s="26" t="n"/>
+      <c r="C97" s="26" t="n"/>
+      <c r="D97" s="26" t="n"/>
+      <c r="E97" s="26" t="n"/>
+      <c r="F97" s="26" t="n"/>
+      <c r="G97" s="26" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="25" t="inlineStr">
+        <is>
+          <t>SL092</t>
+        </is>
+      </c>
+      <c r="B98" s="28" t="n"/>
+      <c r="C98" s="28" t="n"/>
+      <c r="D98" s="28" t="n"/>
+      <c r="E98" s="28" t="n"/>
+      <c r="F98" s="28" t="n"/>
+      <c r="G98" s="28" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="25" t="inlineStr">
+        <is>
+          <t>SL093</t>
+        </is>
+      </c>
+      <c r="B99" s="26" t="n"/>
+      <c r="C99" s="26" t="n"/>
+      <c r="D99" s="26" t="n"/>
+      <c r="E99" s="26" t="n"/>
+      <c r="F99" s="26" t="n"/>
+      <c r="G99" s="26" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="25" t="inlineStr">
+        <is>
+          <t>SL094</t>
+        </is>
+      </c>
+      <c r="B100" s="28" t="n"/>
+      <c r="C100" s="28" t="n"/>
+      <c r="D100" s="28" t="n"/>
+      <c r="E100" s="28" t="n"/>
+      <c r="F100" s="28" t="n"/>
+      <c r="G100" s="28" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="25" t="inlineStr">
+        <is>
+          <t>SL095</t>
+        </is>
+      </c>
+      <c r="B101" s="26" t="n"/>
+      <c r="C101" s="26" t="n"/>
+      <c r="D101" s="26" t="n"/>
+      <c r="E101" s="26" t="n"/>
+      <c r="F101" s="26" t="n"/>
+      <c r="G101" s="26" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="25" t="inlineStr">
+        <is>
+          <t>SL096</t>
+        </is>
+      </c>
+      <c r="B102" s="28" t="n"/>
+      <c r="C102" s="28" t="n"/>
+      <c r="D102" s="28" t="n"/>
+      <c r="E102" s="28" t="n"/>
+      <c r="F102" s="28" t="n"/>
+      <c r="G102" s="28" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="25" t="inlineStr">
+        <is>
+          <t>SL097</t>
+        </is>
+      </c>
+      <c r="B103" s="26" t="n"/>
+      <c r="C103" s="26" t="n"/>
+      <c r="D103" s="26" t="n"/>
+      <c r="E103" s="26" t="n"/>
+      <c r="F103" s="26" t="n"/>
+      <c r="G103" s="26" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="25" t="inlineStr">
+        <is>
+          <t>SL098</t>
+        </is>
+      </c>
+      <c r="B104" s="28" t="n"/>
+      <c r="C104" s="28" t="n"/>
+      <c r="D104" s="28" t="n"/>
+      <c r="E104" s="28" t="n"/>
+      <c r="F104" s="28" t="n"/>
+      <c r="G104" s="28" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="25" t="inlineStr">
+        <is>
+          <t>SL099</t>
+        </is>
+      </c>
+      <c r="B105" s="26" t="n"/>
+      <c r="C105" s="26" t="n"/>
+      <c r="D105" s="26" t="n"/>
+      <c r="E105" s="26" t="n"/>
+      <c r="F105" s="26" t="n"/>
+      <c r="G105" s="26" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="25" t="inlineStr">
+        <is>
+          <t>SL100</t>
+        </is>
+      </c>
+      <c r="B106" s="28" t="n"/>
+      <c r="C106" s="28" t="n"/>
+      <c r="D106" s="28" t="n"/>
+      <c r="E106" s="28" t="n"/>
+      <c r="F106" s="28" t="n"/>
+      <c r="G106" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C7:C106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>ListPT</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.62" bottom="0.55" header="0.28" footer="0.25"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Tahoma"&amp;8 مازندشت — سامانه حساب‌های بانکی&amp;C&amp;"Tahoma"&amp;8 دفتر فروشندگان (خریداران-بازفروش‌ها) — منبع کد حساب در فایل فروش&amp;R&amp;"Tahoma"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Tahoma"&amp;7 باغدشت، بخش مرکزی، شهرستان قائم‌شهر، استان مازندران، ایران&amp;C&amp;"Tahoma"&amp;8 صفحه &amp;P از &amp;N&amp;R&amp;"Tahoma"&amp;7 چاپ: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
@@ -10153,7 +12367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D32"/>
@@ -10811,7 +13025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D32"/>
@@ -11550,7 +13764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0090A4AE"/>
@@ -11784,12 +13998,12 @@
       </c>
       <c r="B14" s="28" t="inlineStr">
         <is>
-          <t>سایر</t>
+          <t>واسطه</t>
         </is>
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>سایر</t>
+          <t>مشتری</t>
         </is>
       </c>
       <c r="D14" s="28" t="n"/>
@@ -11800,8 +14014,16 @@
           <t>PT09</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="26" t="n"/>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>مشتری نقدی</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>مشتری</t>
+        </is>
+      </c>
       <c r="D15" s="26" t="n"/>
     </row>
     <row r="16">
@@ -11810,8 +14032,16 @@
           <t>PT10</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="28" t="n"/>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>سایر</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>سایر</t>
+        </is>
+      </c>
       <c r="D16" s="28" t="n"/>
     </row>
     <row r="17">
@@ -11933,305 +14163,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0090A4AE"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>مازندشت — سورتینگ و بسته‌بندی مرکبات</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>باغدشت، بخش مرکزی، شهرستان قائم‌شهر، استان مازندران، ایران</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>انواع تراکنش (قابل توسعه برای ماهیت‌های آینده)</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="n"/>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>ستون نوع تراکنش در Entry فقط اطلاعاتی/تحلیلی است؛ واریز و برداشت از ستون‌های مبلغ خوانده می‌شود. در آینده می‌توانید ماهیت‌های تازه (انتقال، اصلاحیه و…) تعریف کنید.</t>
-        </is>
-      </c>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>کد</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>عنوان</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>تأثیر بر مانده</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>توضیح</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>Balance Effect</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>T01</t>
-        </is>
-      </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>واریز</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>افزایش مانده</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>برداشت</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>کاهش مانده</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>T03</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>انتقال بین بانکی</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>خنثی در مجموع</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>T04</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>اصلاحیه / تعدیل</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>طبق ماهیت</t>
-        </is>
-      </c>
-      <c r="D10" s="28" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>T05</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>سایر</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>طبق ماهیت</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>T06</t>
-        </is>
-      </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>T08</t>
-        </is>
-      </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>T09</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="28" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="26" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="B18" s="28" t="n"/>
-      <c r="C18" s="28" t="n"/>
-      <c r="D18" s="28" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>T13</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="26" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>T14</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="n"/>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.35" right="0.35" top="0.62" bottom="0.55" header="0.28" footer="0.25"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;"Tahoma"&amp;8 مازندشت — سامانه حساب‌های بانکی&amp;C&amp;"Tahoma"&amp;8 انواع تراکنش (قابل توسعه برای ماهیت‌های آینده)&amp;R&amp;"Tahoma"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Tahoma"&amp;7 باغدشت، بخش مرکزی، شهرستان قائم‌شهر، استان مازندران، ایران&amp;C&amp;"Tahoma"&amp;8 صفحه &amp;P از &amp;N&amp;R&amp;"Tahoma"&amp;7 چاپ: &amp;D</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>